--- a/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
+++ b/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
+++ b/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
+++ b/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
+++ b/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
+++ b/docs/CodeSystem-artemis-prototype-devices-cs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="153">
   <si>
     <t>Property</t>
   </si>
@@ -25,13 +25,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/artemis-prototype-devices-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/artemis-prototype-devices-cs</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,13 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Developmental and test hardware not yet flight-certified (demo units, ground analogs, next-gen prototypes)</t>
+    <t>Developmental and test hardware not yet flight-certified: demo units, ground analogs, next-generation prototypes, and planned LunaNet, surface mobility, habitat, logistics, ISRU, and surface power infrastructure elements</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -94,12 +94,12 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>34</t>
   </si>
   <si>
     <t>Code</t>
@@ -139,22 +139,22 @@
     <t>deviceType</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/artemis-prototype-devices-cs#deviceType</t>
-  </si>
-  <si>
-    <t>Device category (spacecraft, suit, vehicle, habitat, equipment)</t>
-  </si>
-  <si>
-    <t>code</t>
+    <t>Device category (suit, life-support, habitat, communications, navigation, medical-equipment, rover, drone, logistics, isru, power)</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>testEnvironment</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/artemis-prototype-devices-cs#testEnvironment</t>
-  </si>
-  <si>
-    <t>Primary test environment (ground, ISS, analog-mission)</t>
+    <t>Primary test environment (ground, iss, analog-mission)</t>
+  </si>
+  <si>
+    <t>manufacturer</t>
+  </si>
+  <si>
+    <t>Device manufacturer or contractor</t>
   </si>
   <si>
     <t>Level</t>
@@ -178,6 +178,51 @@
     <t>Prototype EVA suit used in ground testing or ISS demonstration (not flight-certified). Test env: ground.</t>
   </si>
   <si>
+    <t>nextgen-plss</t>
+  </si>
+  <si>
+    <t>Next-Generation PLSS</t>
+  </si>
+  <si>
+    <t>Next-generation Portable Life Support System under development (for suits beyond Artemis). Test env: ground.</t>
+  </si>
+  <si>
+    <t>biomonitor-wearable</t>
+  </si>
+  <si>
+    <t>BioMonitor Wearable Prototype</t>
+  </si>
+  <si>
+    <t>Experimental biomedical monitoring device (advanced smart garment for astronauts in trial). Test env: ISS.</t>
+  </si>
+  <si>
+    <t>autonomous-medical-unit</t>
+  </si>
+  <si>
+    <t>Autonomous Medical Unit Prototype</t>
+  </si>
+  <si>
+    <t>Prototype diagnostic device or smart medical assistant being evaluated for lunar use. Test env: ground.</t>
+  </si>
+  <si>
+    <t>habitat-test-module</t>
+  </si>
+  <si>
+    <t>Habitat Test Module</t>
+  </si>
+  <si>
+    <t>Ground-based habitat prototype (e.g., 3D-printed habitat analog or Lunar/Mars yard modules). Test env: analog-mission.</t>
+  </si>
+  <si>
+    <t>surface-habitat-module</t>
+  </si>
+  <si>
+    <t>Surface Habitat Module</t>
+  </si>
+  <si>
+    <t>Planned lunar surface habitat infrastructure element. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
     <t>pressurized-rover-proto</t>
   </si>
   <si>
@@ -187,40 +232,247 @@
     <t>Early concept lunar pressurized rover (testing life support and habitat functions on Earth). Test env: ground.</t>
   </si>
   <si>
-    <t>habitat-test-module</t>
-  </si>
-  <si>
-    <t>Habitat Test Module</t>
-  </si>
-  <si>
-    <t>Ground-based habitat prototype (e.g., 3D-printed habitat analog or Lunar/Mars yard modules). Test env: analog-mission.</t>
-  </si>
-  <si>
-    <t>nextgen-plss</t>
-  </si>
-  <si>
-    <t>Next-Generation PLSS</t>
-  </si>
-  <si>
-    <t>Next-generation Portable Life Support System under development (for suits beyond Artemis). Test env: ground.</t>
-  </si>
-  <si>
-    <t>biomonitor-wearable</t>
-  </si>
-  <si>
-    <t>BioMonitor Wearable Prototype</t>
-  </si>
-  <si>
-    <t>Experimental biomedical monitoring device (advanced smart garment for astronauts in trial). Test env: ISS.</t>
-  </si>
-  <si>
-    <t>autonomous-medical-unit</t>
-  </si>
-  <si>
-    <t>Autonomous Medical Unit Prototype</t>
-  </si>
-  <si>
-    <t>Prototype diagnostic device or smart medical assistant being evaluated for lunar use. Test env: ground.</t>
+    <t>crewed-ltv</t>
+  </si>
+  <si>
+    <t>Crewed LTV</t>
+  </si>
+  <si>
+    <t>Crewed Lunar Terrain Vehicle variant under development. Manufacturer: NASA / Industry Team. Test env: ground.</t>
+  </si>
+  <si>
+    <t>uncrewed-ltv</t>
+  </si>
+  <si>
+    <t>Uncrewed LTV</t>
+  </si>
+  <si>
+    <t>Uncrewed (teleoperated) Lunar Terrain Vehicle variant under development. Manufacturer: NASA / Industry Team. Test env: ground.</t>
+  </si>
+  <si>
+    <t>advanced-ltv</t>
+  </si>
+  <si>
+    <t>Advanced LTV</t>
+  </si>
+  <si>
+    <t>Advanced Lunar Terrain Vehicle concept. Manufacturer: NASA / Industry Team. Test env: ground.</t>
+  </si>
+  <si>
+    <t>ltv-gen-2</t>
+  </si>
+  <si>
+    <t>LTV Generation 2</t>
+  </si>
+  <si>
+    <t>Second-generation Lunar Terrain Vehicle concept. Manufacturer: NASA / Industry Team. Test env: ground.</t>
+  </si>
+  <si>
+    <t>excavator-rover</t>
+  </si>
+  <si>
+    <t>Excavator Rover</t>
+  </si>
+  <si>
+    <t>Lunar surface excavation rover under development. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>site-prep-logistics-rover</t>
+  </si>
+  <si>
+    <t>Site Preparation and Logistics Rover</t>
+  </si>
+  <si>
+    <t>Rover concept for site preparation and logistics tasks. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>international-partner-rover</t>
+  </si>
+  <si>
+    <t>International Partner Rover</t>
+  </si>
+  <si>
+    <t>Partner-provided lunar rover under development. Manufacturer: International Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>science-rover</t>
+  </si>
+  <si>
+    <t>Science Rover</t>
+  </si>
+  <si>
+    <t>Lunar surface science rover concept. Manufacturer: NASA / Partners. Test env: analog-mission.</t>
+  </si>
+  <si>
+    <t>moonfall-drone</t>
+  </si>
+  <si>
+    <t>MoonFall Drone</t>
+  </si>
+  <si>
+    <t>Lunar surface aerial or descent support drone concept. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>orbital-comm-relay</t>
+  </si>
+  <si>
+    <t>Orbital Communication Relay</t>
+  </si>
+  <si>
+    <t>Orbital relay satellite for lunar communications. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>observation-satellite</t>
+  </si>
+  <si>
+    <t>Observation Satellite</t>
+  </si>
+  <si>
+    <t>Lunar observation and monitoring satellite. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>relay-satellite-observability</t>
+  </si>
+  <si>
+    <t>Relay Satellite with Observability</t>
+  </si>
+  <si>
+    <t>Relay satellite with observability functions. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>surface-comm-nav-node</t>
+  </si>
+  <si>
+    <t>Surface Communication and Navigation Node</t>
+  </si>
+  <si>
+    <t>Lunar surface communication and navigation infrastructure node. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>deployable-surface-comm-tower</t>
+  </si>
+  <si>
+    <t>Deployable Surface Communication Tower</t>
+  </si>
+  <si>
+    <t>Deployable surface communications tower. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>high-throughput-surface-comms</t>
+  </si>
+  <si>
+    <t>High-Throughput Surface Communications Node</t>
+  </si>
+  <si>
+    <t>High-bandwidth lunar surface communications node. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>lunar-pnt-node</t>
+  </si>
+  <si>
+    <t>Lunar PNT Node</t>
+  </si>
+  <si>
+    <t>Positioning, navigation, and timing infrastructure node. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>clock-demo-node</t>
+  </si>
+  <si>
+    <t>Lunar Clock Demonstration Node</t>
+  </si>
+  <si>
+    <t>Surface timing and synchronization demonstrator. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>navigation-capability-node</t>
+  </si>
+  <si>
+    <t>Navigation Capability Node</t>
+  </si>
+  <si>
+    <t>Lunar navigation infrastructure element. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>logistics-demo-unit</t>
+  </si>
+  <si>
+    <t>Logistics Demonstration Unit</t>
+  </si>
+  <si>
+    <t>Demonstrator for lunar surface logistics. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>logistics-delivery-vehicle</t>
+  </si>
+  <si>
+    <t>Logistics Delivery Vehicle</t>
+  </si>
+  <si>
+    <t>Lunar surface or cargo delivery logistics asset concept. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>cargo-return-vehicle</t>
+  </si>
+  <si>
+    <t>Cargo Return Vehicle</t>
+  </si>
+  <si>
+    <t>Vehicle concept for returning cargo from lunar surface operations. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>isru-plant</t>
+  </si>
+  <si>
+    <t>ISRU Plant</t>
+  </si>
+  <si>
+    <t>In Situ Resource Utilization processing system under development. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>solar-power-augmentation-unit</t>
+  </si>
+  <si>
+    <t>Solar Power Augmentation Unit</t>
+  </si>
+  <si>
+    <t>Solar power augmentation infrastructure. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>solar-battery-rfc-power-unit</t>
+  </si>
+  <si>
+    <t>Solar Battery RFC Power Unit</t>
+  </si>
+  <si>
+    <t>Solar, battery, and regenerative fuel cell power system. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>fission-surface-power-unit</t>
+  </si>
+  <si>
+    <t>Fission Surface Power Unit</t>
+  </si>
+  <si>
+    <t>Lunar surface fission power system under development. Manufacturer: NASA / DOE / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>power-infrastructure-node</t>
+  </si>
+  <si>
+    <t>Power Infrastructure Node</t>
+  </si>
+  <si>
+    <t>Surface electrical power infrastructure node. Manufacturer: NASA / Partners. Test env: ground.</t>
+  </si>
+  <si>
+    <t>power-distribution-node</t>
+  </si>
+  <si>
+    <t>Power Distribution Node</t>
+  </si>
+  <si>
+    <t>Surface power distribution system. Manufacturer: NASA / Partners. Test env: ground.</t>
   </si>
 </sst>
 </file>
@@ -467,14 +719,16 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -530,7 +784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -551,28 +805,36 @@
       <c r="A2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B2" s="2"/>
+      <c r="C2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="D3" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="C3" t="s" s="2">
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>43</v>
+      <c r="D4" t="s" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +844,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -683,6 +945,398 @@
         <v>68</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
